--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D280BD-026E-4DC3-AD60-1055C80A082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24C6DF8-78DC-4CEB-8780-58CBB950E764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>Município</t>
   </si>
@@ -76,6 +76,18 @@
   </si>
   <si>
     <t>NEOENERGIA PERNAMBUCO</t>
+  </si>
+  <si>
+    <t>Conceição</t>
+  </si>
+  <si>
+    <t>Brejo do Cruz</t>
+  </si>
+  <si>
+    <t>São José do Sabugi</t>
+  </si>
+  <si>
+    <t>São José de Espinharas</t>
   </si>
 </sst>
 </file>
@@ -127,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,7 +148,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.5546875" customWidth="1"/>
@@ -496,11 +507,64 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24C6DF8-78DC-4CEB-8780-58CBB950E764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC3F160-0E8E-4433-AE06-15F7D19DAFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>Município</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>São José de Espinharas</t>
+  </si>
+  <si>
+    <t>São Bento</t>
   </si>
 </sst>
 </file>
@@ -563,6 +566,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
     </row>

--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC3F160-0E8E-4433-AE06-15F7D19DAFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455A526E-7C83-4673-9DB9-98069ED327D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
   <si>
     <t>Município</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>São Bento</t>
+  </si>
+  <si>
+    <t>Capim</t>
   </si>
 </sst>
 </file>
@@ -580,6 +583,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12" s="3"/>
     </row>

--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Municipios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455A526E-7C83-4673-9DB9-98069ED327D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29760AA1-8BAC-445B-AB92-D1D4CC4BD096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
   <si>
     <t>Município</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Brejo do Cruz</t>
   </si>
   <si>
-    <t>São José do Sabugi</t>
-  </si>
-  <si>
     <t>São José de Espinharas</t>
   </si>
   <si>
@@ -94,13 +91,19 @@
   </si>
   <si>
     <t>Capim</t>
+  </si>
+  <si>
+    <t>Paulista</t>
+  </si>
+  <si>
+    <t>São José de Sabugi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,14 +113,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -145,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -153,7 +148,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,7 +537,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -557,7 +551,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -571,7 +565,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -585,20 +579,31 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C12" s="3"/>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
